--- a/assets/Unfinished_data_collection.xlsx
+++ b/assets/Unfinished_data_collection.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Mindsets" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,49 +15,23 @@
     <sheet name="Titel" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <charset val="1"/>
-      <family val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -81,54 +55,21 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -201,41 +142,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -243,176 +184,284 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mindset_ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="2150" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>The Explorer</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Charakter: Explorers sind sehr aktive Lernende und haben keine Angst vor Neuem. Sie informieren sich aktiv, sind vielseitig interessiert, probieren vieles aus und sind an verschiedenen Lernerfahrungen und Themen interessiert. Sie betrachten jede Erfahrung als wertvoll, auch wenn im Moment nicht klar ist, wofür sie gut ist. Für Explorers ist klar, dass sie irgendwann im Leben davon profitieren können.
 Motivationen und Treiber: Explorers wollen im Job up to date sein, z.B. betreffend Technologie und Software. Sie wollen ihr eigenes Humankapital erhalten, um im Beruf relevant und gefragt zu bleiben. Unterstützung vom Arbeitgeber in Form von Geld und Zeit für Weiterbildungen schätzen sie.
@@ -420,18 +469,18 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="2955.95" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>The Experiencer</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Charakter: Für Experiencers steht Spass und Genuss beim Lernen im Vordergrund. Sie glauben, dass sie nur dann offen sind für Lernerfahrungen, wenn sie dabei Freude und Genuss erleben. Sie gehen beim Lernen intuitiv vor und sind sehr praxisorientiert. Für sie ist Lernen vor allem "Learning by doing". Sie lernen gern im Austausch mit anderen, um dabei selbst neue Perspektiven zu erhalten. Experiencers suchen bewusstn den Ausgleich zur Arbeit durch Sabbaticals, Workation im Ausland und Teilzeitarbeit, um ihren Interessen nachzugehen und Abwechslung zu erhalten.
 Motivationen und Treiber: Für Experiencers müssen Lerninhalte direkt in Projekten anwendbar sein, z.B. indem sie mehr Zeit in einem Projekt erhalten, um ein neues Tool zu lernen oder sich in einer neuen Rolle versuchen zu können. Sie schätzen die Zusammenarbeit mit anderen, um im direkten Austausch voneinander und gemeinsam lernen zu können. Für Experiencers muss Lernen lust- und genussvoll sein und Spass machen.
@@ -439,18 +488,18 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="2851.45" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>The Strategist</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Charakter: Strategists sind sehr zielgerichtet und in Bezug auf Lernen formal orientiert. Sie verstehen Lernen als Schlüssel, um beruflich weiterzukommen und beziehen es stark auf formale Weiterbildungen. Lernen hat für sie eine klare Funktion, die auch zielstrebig verfolgt wird. Experiencers erachten lebenslanges Lernen als sehr wichtig und betrachten Lernen auch als Selbstzweck. Für sie ist klar, dass sie immer weiter lernen werden, ohne jetzt schon zu wissen, was genau es sein wird.
 Motivationen und Treiber: Strategists wollen zielstrebig weiterkommen und ihre Lernaktivitäten mit anerkannten Abschlüssen auf dem Arbeitsmarkt vorweisen können. Entsprechend ist ihnen die Qualität und Anerkennung von Lernangeboten wichtig. Strategists holen sich aktiv Inputs von aussen oder initiieren den Austausch im Team selbst. Sie brauchen eine klare Struktur und Druck, um zu Lernen (z.B. in einem Masterprogramm).
@@ -458,18 +507,18 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="2388.8" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>M04</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>The Sensemaker</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Charakter: Sensemakers wollen sich selbst und die Welt um sich herum genau verstehen. Sie haben ein sehr breites und ganzheitliches Verständnis von Lernen. Sie ziehen aus jeder Erfahrung ein "learning" und reflektieren Fehler und Erfahrungen bewusst, um etwas daraus zu lernen. Sensemakers suchen aktiv den Perspektivenwechsel durch den Austausch mit anderen und betonen das Gemeinsame.
 Motivationen und Treiber: Sensemakers lernen vor allem, um komplexe Zusammenhänge ganzheitlich zu verstehen, zu interpretieren und einordnen zu können. Dazu wollen sie verschiedene Perspektiven integrieren und Menschen um sich haben, mit denen sie sich austauschen können.
@@ -478,3378 +527,3393 @@
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Frage_ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Frage</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Kontext</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>F01</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Was ist Lernen für dich?</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Bedeutung: Als Einstiegsfrage dient diese Frage dazu, generell die Bedeutung des Lernens für die Besucher*innen zu erfassen. Es geht darum herauszufinden, ob die Besucher*innen ein sehr breites Verständnis von Lernen haben oder Lernen eher eng fassen und mit Schulen, Kursen oder Weiterbildungen in Verbindung bringen.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Warum lernst du?</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Motivation: Alle Menschen lernen, und zwar in jedem Alter, aber sie haben ganz unterschiedliche Motivationen, zu lernen. Diese Frage zielt drauf ab, die Motivationen und Treiber zu verstehen, warum jemand lernt.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>F03</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Wie lernst du am besten?</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Formen: Es gibt ganz unterschiedliche Formen des Lernens – klassisch formal in Kursen und Weiterbildungen, oder eher beim Machen. Bei dieser Frage geht es darum zu erfahren, wie jemand am besten lernt.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Wie reagierst du, wenn du unsicher bist?</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Verhalten bei Unsicherheit: Lernen ist per se eine unangenehme Situation, weil man sich Unsicherheit aussetzt, Feedback erhält oder nicht weiss, wie etwas funktioniert. Man ist dann nicht in der "Performance Zone", wo man machen kann, was man am besten kann, sondern in der "Learning Zone", wo man wächst und etwas Neues lernt. Diese Frage zielt darauf ab, wie Menschen darauf reagieren, wenn sie sich in der "Learning Zone" bewegen.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>F05</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Was braust du, um im Alltag zu lernen?</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bedürfnis: Viele Menschen würden gern mehr lernen und betrachten Lernen als sehr wichtig. In der Realität sind sie aber mit Hürden konfrontiert wie z.B. zu wenig Zeit zum Lernen oder fehlende Orientierung, was sie überhaupt lernen bzw. worauf sie sich fokussieren sollen. Diese Frage zielt darauf ab zu verstehen, was das grösste Bedürfnis in Bezug auf Lernen im Alltag ist.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F06</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Wo stehst du gerade im Berufsleben?</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Aktuelle Situation: Der Kontext der Menschen spielt beim Lernen und beruflicher Entwicklung eine grosse Rolle. Ob jemand am Anfang des Berufslebens steht oder bereits am Ende ist, ob jemand mittendrin und angekommen ist oder offen für Neues ist. Bei dieser Frage geht es darum zu verstehen, wo im Berufsleben eine Person gerade steht, um ihr anschliessend passende Angebote und Ressourcen vorzuschlagen.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="48.58" customWidth="1" style="6" min="5" max="5"/>
-    <col width="33.5" customWidth="1" style="6" min="9" max="9"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Antwort_ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Frage_ID</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Frage</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>RFID_Tag_ID</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Antwort</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Kontext</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Mindsets</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>svg</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>F01</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Was ist Lernen für dich?</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E03F860</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E03F860, E28069150000600B3E047860</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Fast alles</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Person hat ein sehr breites Verständnis von lernen und interpretiert praktisch jede Lebens- und Arbeitserfahrung als Möglichkeit, zu lernen. Die Person sieht auch Umwege, Misserfolge und gescheiterte Versuche als positive Erfahrung an, oft wird dies aber erst im Nachhinein klar.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Explorer, Sensemaker</t>
         </is>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>semioval_f01</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>F01</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Was ist Lernen für dich?</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>E28069150000700B3E03E860</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Wie ein Werkzeugkasten</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Person versteht Lernen als Sammlung von Wissen, Fähigkeiten und Erfahrungen, aus denen man sich bedienen kann.</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Strategist</t>
         </is>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>wide_rectangle_f01</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>F01</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Was ist Lernen für dich?</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E03F460</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E03F460, E28069150000600B3E049C60</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Wie ein Spiegel</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Person lernt stark im Austausch mit anderen und indem Erlebnisse und Erfahrungen reflektiert werden. Person sucht aktiv nach Lernmöglichkeiten und bezieht andere Perspektiven mit ein, um die eigene Sicht zu challengen und daraus etwas zu lernen.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Sensemaker</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>capsule_pill_f01</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>A04</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>F01</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Was ist Lernen für dich?</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>E28069150000600B3E03D060</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Wie ein Labor</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Person ist experimentierfreudig und probiert gerne aus. "Learning by doing" steht im Vordergrund. Die Person hat keine Angst vor Unbekanntem.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Experiencer, Explorer</t>
         </is>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>flat_pyramid_f01</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A05</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>F01</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Was ist Lernen für dich?</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>E28069150000600B3E03EC60</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Schule und Kurse</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Die Person ist stark formal orientiert und hat ein klassisches Verständnis von Lernen. Die Person ist zielgerichtet und möchte zu recht, dass Lernaktivitäten offiziell anerkannt werden und auf dem Arbeitsmarkt sichtbar sind.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Strategist</t>
         </is>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>wide_rectangle_f01</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>F01</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Was ist Lernen für dich?</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000700B3E03F060</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>E28069150000700B3E03F060, E28069150000600B3E046C60</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Weiss nicht</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Die Person hat sich noch keine Gedanken darüber gemacht, was Lernen für sie bedeutet. Sie ist lernt die ganze Zeit, jedoch nicht bewusst und bezeichnet es auch nicht als solches, was auf einen sehr unverkrampften und lockeren Umgang damit schliessen lässt.</t>
         </is>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>flat_trapezoid_f01</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A07</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Warum lernst du?</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000700B3E03D460</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>E28069150000700B3E03D460, E28069150000700B3E046860</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Um am Ball zu bleiben</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Wichtigste Motivation ist, im Job relevant zu bleiben und den Anschluss nicht zu verlieren. Die Arbeitswelt entwickelt sich in rasantem Tempo und die Person will dabei up to date bleiben.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Explorer, Strategist</t>
         </is>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>tall_pyramid_f02</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A08</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Warum lernst du?</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000700B3E040460</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>E28069150000700B3E040460, E28069150000700B3E047C60</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Um mich zu entwickeln</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Persönliche Entwicklung ist ein starker Treiber und auch nicht auf das Arbeitsumfeld beschränkt. Person ist stark intrinsisch motiviert, sich persönlich weiterzuentwickeln, sei es im Job oder auch daneben.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Explorer, Experiencer Sensemaker, Strategist</t>
         </is>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>rhombus_udlr_f02</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A09</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Warum lernst du?</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E040060</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E040060, E28069150000600B3E047460</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Um Dinge zu verstehen</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Wichtigster Treiber ist es, sich selbst und die Welt um sich herum besser zu verstehen. Die Person möchte den Dingen auf den Grund gehen und geht mit offenen Augen durchs Leben. Der Austausch mit anderen ist wichtig, um durch  verschiedene Perspektiven das eigene Erleben zu hinterfragen.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Sensemaker</t>
         </is>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>upright_pill_f02</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A10</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Warum lernst du?</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>E28069150000700B3E03FC60</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Um Fähigkeiten zu erweitern</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Die Motivation zu lernen ist stark auf spezifische Fähigkeiten und Tools fokussiert, vor allem im Arbeitskontext.</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Explorer, Experiencer Sensemaker, Strategist</t>
         </is>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>double_upright_pill_f02</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A11</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Warum lernst du?</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>E28069150000700B3E040860</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Um einen Abschluss zu machen</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Der Treiber ist ein anerkannter Abschluss, ein Zertifikat oder ein bestimmter Titel. Treiber fürs Lernen ist hier strategisch und taktisch.</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Strategist</t>
         </is>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>stacked_circles_f02</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A12</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>F03</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Wie lernst du am besten?</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E040C60</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E040C60, E28069150000700B3E045860</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Durch Machen</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Die Person lernt intuitiv durch das Machen. Learning by doing steht im Vordergrund. Praxis und eigene Erfahrung ist wichtiger als Theorie.</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Experiencer</t>
         </is>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>stepped_block_3_f03</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A13</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>F03</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Wie lernst du am besten?</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000700B3E041060</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>E28069150000700B3E041060, E28069150000700B3E048060</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Im Austausch</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Die Person lernt stark im Austausch mit anderen und im Team. Sie sucht aktiv nach Feedback und holt sich Hilfe, wenn sie nicht weiter weiss.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Sensemaker, Explorer</t>
         </is>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>stacked_circles_custom_f03</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="4">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A14</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>F03</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Wie lernst du am besten?</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000700B3E03D860</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>E28069150000700B3E03D860, E28069150000600B3E048860</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Mit Struktur</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Die Person braucht Struktur und Druck von aussen, um gut zu lernen. Sie lernt am effektivsten in einem Programm, in dem es Deadlines und Kontrollen gibt.</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Strategist</t>
         </is>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>rhombus_udlr_f03</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="4">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A15</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>F03</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Wie lernst du am besten?</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>E28069150000700B3E044060</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Durch Beobachten</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Die Person hat gerne einen Input oder eine Person, die sie beobachten kann, bevor sie selbst macht. Sie möchte zuerst wissen, wie es geht, bevor sie sich selbst ans Werk macht.</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Explorer</t>
         </is>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>tall_trapezoid_f03</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="4">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A16</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>F03</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Wie lernst du am besten?</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>E28069150000600B3E044460</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Weiss nicht</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Die Person macht sich keine Gedanken darüber, wie und wann sie im Alltag lernt, es passiert unbewusst. Sie hat auch keine Klarheit darüber, welches Lernformat ihr am ehesten zusagt.</t>
         </is>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>facing_bowls_f03</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="4">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A17</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Wie reagierst du, wenn du unsicher bist?</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000700B3E041C60</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>E28069150000700B3E041C60, E28069150000600B3E049060</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Ausweichen</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Die Person weicht Unsicherheiten tendenziell aus oder vermeidet sie.</t>
         </is>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>wide_rectangle_f04_1</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="4">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A18</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Wie reagierst du, wenn du unsicher bist?</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>E28069150000600B3E041460</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Beobachten</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Die Person beobachtet die Situation zuerst, bevor sie sich an jemanden wendet oder das Problem selbst zu lösen versucht.</t>
         </is>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>wide_rectangle_f04_2</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="4">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A19</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Wie reagierst du, wenn du unsicher bist?</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>E28069150000700B3E042060</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Ausprobieren</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Die Person hat keine Angst vor Fehlern oder Unsicherheiten und geht das Problem tendenziell proaktiv an.</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Experiencer, Explorer</t>
         </is>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>wide_rectangle_f04_3</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="4">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A20</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Wie reagierst du, wenn du unsicher bist?</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>E28069150000600B3E03E060</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Analysieren</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Die Person möchte alle Fakten kennen, bevor sie etwas ausprobiert. Sie wägt genau ab und möchte es "richtig" machen.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Sensemaker</t>
         </is>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>wide_rectangle_f04_4</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="4">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A21</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Wie reagierst du, wenn du unsicher bist?</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E042460</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E042460, E28069150000700B3E048C60</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Fragen</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Die Person holt sich aktiv Hilfe oder bindet bewusst andere Perspektiven ein, um eine Unsicherheit oder ein Problem zu überwinden.</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>wide_rectangle_f04_5</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="4">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A22</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Wie reagierst du, wenn du unsicher bist?</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E041860</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E041860, E28069150000700B3E049460</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Reden</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Die Person spricht mit vertrauten Personen darüber. Nicht unbedingt, um Ratschläge zu erhalten, sondern mehr als Strategie, um eine Unsicherheit zu überwinden.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Sensemaker</t>
         </is>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" t="n">
         <v>4</v>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>wide_rectangle_f04_6</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="4">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A23</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>F05</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Was braust du, um im Alltag zu lernen?</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E045060</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E045060, E28069150000600B3E046060</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Zeit</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Die Person hat zu wenig Zeit, um Lernaktivitäten in ihren Alltag einzubauen. Der Grund ist, dass Menschen bei der Arbeit unter hohem Effizienz- und Produktivitätsdruck stehen und immer performen müssen. Es bleibt kaum Zeit, um neue Programme oder Features zu lernen oder sich in ein Thema zu vertiefen.</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Experiencer, Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" t="n">
         <v>5</v>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>sphere_circle_f05</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="4">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A24</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>F05</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Was braust du, um im Alltag zu lernen?</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>E28069150000600B3E044860</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Unterstützung</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Der Person fehlt Unterstützung in Form von Zeit oder Geld vom Arbeitgeber. Oder ein Angebot/Programm, das ihr dabei hilft, Neues zu lernen oder eine Veränderung anzustossen.</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Explorer</t>
         </is>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" t="n">
         <v>5</v>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>sphere_circle_f05</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="4">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A25</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>F05</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Was braust du, um im Alltag zu lernen?</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>E28069150000700B3E045460</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Orientierung</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Die Person braucht Orientierung, in welche Richtung sie sich entwickeln soll oder worauf sie ihre Lernaktivitäten fokussieren soll. Das Weiterbildungsangebot ist so gross und die Möglichkeiten endlos, sodass es oft schwer fällt, sich zu entscheiden.</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Explorer</t>
         </is>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>sphere_circle_f05</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="4">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A26</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>F05</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Was braust du, um im Alltag zu lernen?</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E043C60</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E043C60, E28069150000600B3E045C60</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Motivation</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Die Person hat keine Motivation oder Energie, sich über die eigentliche Arbeit hinaus noch mit weiteren Themen zu beschäftigen. Viele sind durch die vielen Kommunikationskanäle bei der Arbeit und die ständige Erreichbarkeit müde, und wollen sich in ihrer Freizeit erholen anstatt sich noch mit weiteren Themen zu befassen.</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Experiencer</t>
         </is>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>sphere_circle_f05</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="4">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A27</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>F05</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Was braust du, um im Alltag zu lernen?</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E03DC60</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E03DC60, E28069150000700B3E046460</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>Safe Space</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Die Person braucht ein sicheres Umfeld, in dem sie ausprobieren und Fehler machen kann. Ausserdem braucht sie vertrauensvolle Personen, mit denen sie sich offen austauschen und gemeinsam lernen kann.</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" t="n">
         <v>5</v>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>sphere_circle_f05</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="4">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A28</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>F05</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Was braust du, um im Alltag zu lernen?</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>E28069150000700B3E044C60</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Nichts</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Die Person ist zufrieden und hat in Bezug auf das Lernen keine Bedürfnisse oder Hürden im Alltag.</t>
         </is>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
         <v>5</v>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>sphere_circle_f05</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="4">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A29</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>F06</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Wo stehst du gerade im Berufsleben?</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000700B3E043460</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>E28069150000700B3E043460, E28069150000600B3E048460</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>Am Anfang</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Junge Menschen am Anfang ihres Berufslebens. Sie müssen ihre Position in der Arbeitswelt finden und wollen Erfahrung sammeln. Ihre Herausforderung ist es, einen Beruf oder Job zu finden, der zu ihren Stärken, ihrer Haltung und ihren Interessen passt.</t>
         </is>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
         <v>6</v>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>capsule_pill_f06</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="4">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A30</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>F06</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Wo stehst du gerade im Berufsleben?</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000600B3E043060</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>E28069150000600B3E043060, E28069150000700B3E047060</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Mittendrin</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Menschen in der Mitte ihres Berufslebens. Sie haben viele Jahre Berufserfahrung, sind aber oft in der Routine gefangen und suchen nach Abwechslung und Möglichkeiten, aus dem Berufsalltag auszubrechen. Oft sind auch sie sich ihrer Stärken und Interessen gar nicht so klar.</t>
         </is>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
         <v>6</v>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>semioval_f06</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="4">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A31</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>F06</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Wo stehst du gerade im Berufsleben?</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>E28069150000700B3E03E460</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>In einer Veränderung</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Diese Person möchte sich verändern und hat den Prozess bereits angestossen. Veränderungen bringen Unruhe und werfen Fragen auf.</t>
         </is>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
         <v>6</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>flat_pyramid_sockel_f06</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="4">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A32</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>F06</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Wo stehst du gerade im Berufsleben?</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>E28069150000600B3E042860</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Offen für Neues</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Diese Person möchte sich verändern und wägt verschiedene Optionen ab. Sie weiss aber nicht, was als nächstes kommt.</t>
         </is>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
         <v>6</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>stepped_block_f06</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="4">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A33</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>F06</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Wo stehst du gerade im Berufsleben?</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>E28069150000700B3E042C60</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>E28069150000700B3E042C60, E28069150000700B3E049860</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>Auf der Zielgeraden</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Diese Person hat nur noch wenige Jahre bis zum Ruhestand, möchte diese Zeit jedoch sinnvoll verbringen und bis zum Schluss relevant, gefragt und wertgeschätzt bleiben.</t>
         </is>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
         <v>6</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>wide_rectangle_f06</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F56"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="189.83" customWidth="1" style="6" min="2" max="2"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kategorie</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mindsets</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Bedürfnisse</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Situation</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Es lebe der Generalist, von David Epstein. Ein Buch darüber, warum breites statt hyperspezialisiertes Lernen zu erfolgreicheren Karrieren führt.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>https://www.orellfuessli.ch/shop/home/artikeldetails/A1056960585?ProvID=10917735&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=15425760223&amp;gbraid=0AAAAADpVXc47uV9lKfTqilF-IJExZND5u&amp;gclid=Cj0KCQiAx8PKBhD1ARIsAKsmGbc7rV9mM2bfVoXeKfQy2SztPpft1iao3SydUQbXCmWU_hEpCQ522jgaAnzpEALw_wcB</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Explorer, Sensemaker</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Orientierung, Motivation</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Why specializing early doesn't always mean career success, von David Epstein. TED-Talk (ca. 14 Min.) zur Idee, dass vielfältige Erfahrungen langfristig Vorteile bringen.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>https://www.ted.com/talks/david_epstein_why_specializing_early_doesn_t_always_mean_career_success</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Explorer, Experiencer</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Orientierung, Motivation</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>The Reinvention of Normal, von Dominic Wilcox. Ein poetischer Kurzfilm (ca. 8 Min.) über spielerisches Erfinden und das Neu-Denken des Alltäglichen.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>https://vimeo.com/122959827</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Explorer, Experiencer</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Creative Types Test, von Adobe. Online-Persönlichkeitstest, der kreative Stärken sichtbar macht und Impulse für passende Lern- und Arbeitsweisen gibt.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>https://mycreativetype.com</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Orientierung, Safe Space</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Am Anfang, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Beginners, von Tom Vanderbilt. Ein Buch über die Freude und Veränderungskraft des lebenslangen Lernens.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>https://tomvanderbilt.com/books/beginners-the-joy-and-transformative-power-of-lifelong-learning/</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Explorer, Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Out of the Box, von Mathias Morgenthaler. Ein Buch über Geschichten von Menschen mit unkonventionellen Berufswegen.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>https://www.beruf-berufung.ch/impulse/out-of-the-box</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Sensemaker, Explorer</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Orientierung, Motivation</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Make Time, von Jake Knapp &amp; John Zeratsky. Ein Buch darüber, wie man im vollen Alltag Raum fürs Wesentliche schafft.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>https://maketime.blog</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Strategist, Explorer, Experiencer</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Zeit, Unterstützung</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>9 Wege, wie ihr Wissen innerhalb der Organisation austauscht, von Neue Narrative. Ein Artikel über praktische Formate für selbstorganisiertes Lernen im Team und organisationale Wissenskultur.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://www.neuenarrative.de/magazin/neun-wege-wissen-auszutauschen</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Safe Space, Unterstützung</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>I didn’t want a job, von Amie McNee. Ein Video (ca. 13 Min.) über alternative Vorstellungen von Arbeit und eigenständige Lebenswege.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ZydTOTmW_vA</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Motivation, Orientierung, Nichts</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Am Anfang, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Designing Your Life, von Bill Burnett &amp; Dave Evans. Ein Buch über Design-Thinking für Karrierefragen und Experimente für berufliche Neuausrichtung.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://designingyour.life</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Strategist, Explorer, Sensemaker</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Orientierung, Safe Space</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Working Identity, von Herminia Ibarra. Ein Buch über Strategien für Karrieretransitionen und wie man sie für sich selbst nutzen kann.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://herminiaibarra.com/working-identity-book/</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Sensemaker, Strategist, Experiencer, Explorer</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Orientierung, Safe Space</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>In einer Veränderung, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Choiceology, von Katy Milkman &amp; Charles Schwab. Ein Podcast, der uns lehrt, bessere Entscheidungen zu fällen.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://open.spotify.com/show/5eEQ5hd4CfpsYkfZZi136a</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Unterstützung</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Stah da, Phenomden. Ein Song über Gelassenheit, Dankbarkeit und Präsenz im Alltag.</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://open.spotify.com/intl-de/track/2MjgHgShRfe2t1t5R087vQ?si=4a6afef786704b65</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker, Explorer</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Motivation, Nichts</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="4">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Zukunftshelden, von Ben Zaugg. Ein Podcast für alle, die ihre berufliche Gegenwart und Zukunft selber gestalten wollen.</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://open.spotify.com/show/2UeGqLbInObgQ4ogiPgeA2</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Explorer, Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Motivation, Orientierung, Safe Space</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="4">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Atomic Habits, von James Clear. Ein Buch über Mikro-Strategien, um Lern- und andere Gewohnheiten trotz vollem Alltag aufzubauen.</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://jamesclear.com/atomic-habits</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Strategist, Explorer</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Zeit, Motivation</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="4">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>On the Way to New Work, von Christoph Magnussen &amp; Michael Trautmann. Ein Podcast mit Menschen, die Arbeit neu denken.</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://open.spotify.com/show/1wGyQcGHHHvR1T2YycltYE</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Explorer, Sensemaker, Experiencer</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="4">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Tools &amp; Inspiration</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Man lernt nie aus, von Nancy Meyers. Ein Spielfilm, im dem Robert De Niro als 70-jähriger Witwer als Senior-Praktikant nochmals durchstartet.</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://www.netflix.com/ch/title/80047616</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker, Explorer</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Motivation, Safe Space</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="4">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Coursera Career Academy. Eine Plattform für Online-Kurse mit strukturierten Zertifikatsprogrammen für berufliche Neuorientierung, v.a. in Tech und Business.</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://www.coursera.org</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Strategist, Explorer</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Zeit, Orientierung, Unterstützung</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="4">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>The School of Life / Work. Eine Online-Plattform, um das eigene Karrierepotenzial zu entdecken und sowohl Erfolg als auch Sinn in der gewählten Position zu finden.</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>https://www.theschooloflife.com/work/</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Sensemaker, Experiencer, Explorer, Strategist</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Motivation, Orientierung, Safe Space</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Mittendrin, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="4">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Karriereguide Future Jobs Classes der Haufe Akademie. Interaktiver Online-Guide zur Reflexion von Stärken, Trends und nächsten Karriereschritten.</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>https://www.haufe-akademie.de/future-jobs-classes/karriereguide?med=https%3A%2F%2Fwww.perplexity.ai%2F&amp;med=https%3A%2F%2Fwww.perplexity.ai%2F</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Strategist, Explorer</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Orientierung, Unterstützung</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Am Anfang, In einer Veränderung, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="4">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>80,000 Hours. Eine Online-Plattform für Karrieren, die nicht nur erfüllend sind, sondern auch Zukunft gestalten.</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>https://80000hours.org</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Strategist, Sensemaker, Explorer</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Orientierung, Unterstützung</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="4">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Skillshare. Eine Online-Lernplattform mit kreativen Kursen für Anfänger und Profis – von Illustration bis UX/UI Design.</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>https://www.skillshare.com/de/</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Experiencer, Explorer</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Orientierung, Unterstützung</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Auf der Zielgeraden, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="4">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Udemy. Eine Online-Lernplattform für Karriere, Neuorientierung und Skills im KI-Zeitalter.</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>https://www.udemy.com</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Strategist, Explorer</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Zeit, Orientierung, Unterstützung</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="4">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Udacity. Online-Lernplattform für Nanodegree-Programme in Tech und Data mit berufsbezogener Ausrichtung.</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>https://www.udacity.com</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Strategist, Explorer</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Zeit, Orientierung, Unterstützung</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="4">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>LinkedIn Learning. Online-Kurse zu Business, Tech und Kreativthemen mit Integration ins berufliche Profil.</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/learning/</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Strategist, Explorer</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Zeit, Orientierung, Unterstützung</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="4">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Crash Course. Ein YouTube-Kanal mit kostenlosen, niederschwelligen Lernvideos zu vielen Wissensgebieten von Geistes- bis Naturwissenschaften und vieles mehr.</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>https://www.youtube.com/user/crashcourse</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Explorer, Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Motivation, Zeit, Orientierung, Nichts</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="4">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Benevol. Eine Plattform für Freiwilligenarbeit in der Schweiz als Lern- und Erprobungsraum für neue Kompetenzen.</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>https://benevol.ch</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Safe Space, Motivation, Nichts</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Mittendrin, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="4">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Fondation KISS. Nachbarschaftshilfe sowie lokale Tausch- und Unterstützungsangebote für mehr soziale Teilhabe und informelles Lernen.</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>https://fondation-kiss.ch</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Safe Space, Motivation, Nichts</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="4">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Klären Sie Ihre berufliche Situation. 12 kurze Online-Fragebögen für Klarheit und Tipps über die berufliche Situation. Ein Angebot des Schweizerischen Dienstleistungszentrums Berufsbildung (SDBB).</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>https://laufbahn.berufsberatung.ch</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Strategist, Explorer, Sensemaker, Experiencer</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Orientierung, Unterstützung</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="4">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Studien-Interessen-Check SIC. Ein Online-Check, um Interessen zu klären für Studienrichtungen der universitären Hochschulen, Fachhochschulen und Pädagogischen Hochschulen in der Schweiz. Ein Angebot des Schweizerischen Dienstleistungszentrums Berufsbildung (SDBB).</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>https://www.berufsberatung.ch/sic</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Strategist, Explorer, Sensemaker, Experiencer</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Orientierung, Unterstützung</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Am Anfang, In einer Veränderung</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="4">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Explorix (Testverfahren). Wissenschaftliches Tool, um berufliche Perspektiven und Karrierechancen zu entdecken.</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>https://www.explorix.ch</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Strategist, Explorer</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Orientierung, Safe Space</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Am Anfang, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="4">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>viamia. Kostenlose berufliche Standortbestimmung für Erwerbstätige über 40. Ein Beratungsangebot von Bund und Kantonen.</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>https://viamia.ch</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Strategist, Sensemaker, Explorer</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Unterstützung, Orientierung</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="4">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>CareerFoundry. Online-Career-Academy mit Mentoring-basierten Programmen für Quereinstiege in Tech-Berufe.</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>https://careerfoundry.com</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Strategist, Explorer</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Unterstützung, Orientierung</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>In einer Veränderung, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="4">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>OpenLearn, The Open University. Kostenlose Online-Kurse für Erwachsene zu Karriere und Allgemeinbildung.</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>https://www.open.edu/openlearn/</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Explorer, Strategist</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Unterstützung, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="4">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Anlaufstellen &amp; Angebote</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Meetup. Informelle Lern- und Austauschformate zu Karriere, Tech und New Work.</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>https://www.meetup.com/de-DE/</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Experiencer, Explorer, Sensemaker</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Safe Space, Motivation, Unterstützung, Orientierung</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Mittendrin, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="4">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Future Skills Studio: Vom Lehrer zum Digital Learning Designer</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="4">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Future Skills Studio: Von der Ingenieurin zur Green Tech Engineer</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="4">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Future Skills Studio: Von der Verwaltungsangestellten zur Daten Analystin</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="4">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Future Skills Studio: Vom Handwerker zum Migrationsfachmann</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="4">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Future Skills Studio: Vom Projektmanager zum Agile Coach</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="4">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Future Skills Studio: Von der Pflegefachkraft zum Digital Health Coach</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="4">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Future Skills Studio: Von der Grafikdesignerin zur XR-Experience Designerin</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="4">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Peer Workshop für Einsteiger*innen</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Am Anfang</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="4">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Peer Workshop für Aufsteiger*innen</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Mittendrin</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="4">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Peer Workshop für Wiedereinsteiger*innen</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>In einer Veränderung, Offen für Neues</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="4">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Peer Workshop für Umsteiger*innen</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>In einer Veränderung</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="4">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Peer Workshop für Aussteiger*innen</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Experiencer, Sensemaker</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Orientierung, Motivation, Safe Space, Nichts</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="4">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Zunft der Zukunft: Care Economy</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Zeit, Unterstützung</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="4">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Zunft der Zukunft: Zirkuläre Wirtschaft</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Zeit, Unterstützung</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="4">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Zunft der Zukunft: Robotik und Automatisierung</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Zeit, Unterstützung</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="4">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Zunft der Zukunft: KI-gestützte Entscheidungen</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Zeit, Unterstützung</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="4">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Zunft der Zukunft: Nachhaltige Mobilität</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Zeit, Unterstützung</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="4">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Zunft der Zukunft: Digitale Souveränität</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Zeit, Unterstützung</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="4">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Zunft der Zukunft: Bio und Health Tech</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
         <is>
           <t>Explorer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Zeit, Unterstützung</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="4">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Programm-Empfehlung</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Career Pop-up: Walk-in-Beratung bei einem*einer Berufs- und Laufbahncoach</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Explorer, Experiencer, Strategist, Sensemaker</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Zeit, Unterstützung, Orientierung, Safe Space</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Am Anfang, Mittendrin, In einer Veränderung, Offen für Neues, Auf der Zielgeraden</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Prompt</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="1612.65" customHeight="1" s="4">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Du bist eine KI, die personalisierte, poetische, aber bodenständige Kurztexte schreibt. Die Texte werden in einer Ausstellung zu lebenslangem Lernen und beruflichen Transitionen verwendet. Sie erscheinen am Ende einer interaktiven Installation als gedrucktes Feedback für Besucher*innen.
 Die Besucher*innen haben während der Ausstellung mehrere Tokens gesammelt, die zusammen beschreiben:
@@ -3860,8 +3924,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="1358.95" customHeight="1" s="4">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>### Rahmenbedingungen
 - **Länge:** 2 Absätze à jeweils max. **400 Zeichen inkl. Leerzeichen**. Kurze, flüssige Sätze.  
@@ -3873,8 +3937,8 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="1209.7" customHeight="1" s="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t xml:space="preserve">### Kontextbewusstsein
 Diese Texte stehen in einem gesellschaftlichen Rahmen:  
@@ -3883,8 +3947,8 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="3276.75" customHeight="1" s="4">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>### Struktur und inhaltliche Leitlinien
 #### **Absatz 1 (Mindset + Situation):**
@@ -3913,8 +3977,8 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="434.3" customHeight="1" s="4">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>### Eingabevariablen
 &lt;Mindset&gt;: [Name oder Beschreibung des Lerncharakters]  
@@ -3923,8 +3987,8 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="897" customHeight="1" s="4">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>### Ausgabebeispiel
 Eingabe:
@@ -3938,1248 +4002,1244 @@
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B102"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>adjektiv</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Endlos</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Gnadenlos</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Unverschämt</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Unfassbar</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Irre</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Sensationell</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Legendär</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Episch</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Maximal</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Radikal</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Furchtlos</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Absolut</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Hochgradig</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="4">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="4">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Phänomenal</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="4">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Atemberaubend</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="4">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Unschlagbar</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="4">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Frech</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="4">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="4">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Vollgas</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="4">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Verrückt</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="4">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Weltklasse</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="4">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Mega</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="4">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Ziemlich</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="4">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Fix</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="4">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Sagenhaft</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="4">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Grandios</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="4">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Brillant</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="4">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Genial</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="4">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Spektakulär</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="4">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Abgefahren</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>primo</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="4">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>neugierig</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="4">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>wissbegierig</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="4">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="4">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>zukunftsorientiert</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="4">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>lernfreudig</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="4">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>aufgeschlossen</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="4">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>explorativ</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="4">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>aufmerksam</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="4">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>resilient</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="4">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>hungrig</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="4">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>unvoreingenommen</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="4">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>vielseitig</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="4">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>entdeckungsfreudig</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="4">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>inputoffen</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="4">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>chancenorientiert</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="4">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>themenoffen</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="4">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>adaptiv</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="4">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>anschlussfähig</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>explorer</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="4">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>experimentierfreudig</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="4">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>praxisnah</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="4">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>kreativ</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="4">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>fehlertolerant</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="4">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>ideenreich</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="4">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>praxisorientiert</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="4">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>hands-on</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="4">
-      <c r="A58" s="6" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>anwendungsstark</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="4">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>intuitiv</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="4">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>spielerisch</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="4">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>dialogisch</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="4">
-      <c r="A62" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>teamorientiert</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="4">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>austauschfreudig</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="4">
-      <c r="A64" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>kollaborativ</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="4">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>menschenorientiert</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="4">
-      <c r="A66" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>multiperspektivisch</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="4">
-      <c r="A67" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>alltagsnah</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="4">
-      <c r="A68" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>umsetzungsstark</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>experiencer</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="4">
-      <c r="A69" s="6" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>strategisch</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="4">
-      <c r="A70" s="6" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>fokussiert</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="4">
-      <c r="A71" s="6" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>lösungsorientiert</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="4">
-      <c r="A72" s="6" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>strukturiert</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="4">
-      <c r="A73" s="6" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>zielklar</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="4">
-      <c r="A74" s="6" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>zielstrebig</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="4">
-      <c r="A75" s="6" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>systematisch</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="4">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>zielorientiert</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="4">
-      <c r="A77" s="6" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>methodisch</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="4">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>diszipliniert</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="4">
-      <c r="A79" s="6" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>konsequent</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="4">
-      <c r="A80" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>qualitätskritisch</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="4">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>taktisch</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>strategist</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="4">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>transferstark</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="4">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>hinterfragend</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="4">
-      <c r="A84" s="6" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>erkenntnisdurstig</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="4">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>vernetzt</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="4">
-      <c r="A86" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>kombinierend</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="4">
-      <c r="A87" s="6" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>metakognitiv</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="4">
-      <c r="A88" s="6" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>feedbackoffen</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="4">
-      <c r="A89" s="6" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>analytisch</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="4">
-      <c r="A90" s="6" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>kritisch</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1" s="4">
-      <c r="A91" s="6" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>reflektierend</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1" s="4">
-      <c r="A92" s="6" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>selbstreflexiv</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1" s="4">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>ganzheitlich</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1" s="4">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>sinnorientiert</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1" s="4">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>integrativ</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="4">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>perspektivenreich</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="15" customHeight="1" s="4">
-      <c r="A97" s="6" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>dialogoffen</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="15" customHeight="1" s="4">
-      <c r="A98" s="6" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>lernoffen</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="15" customHeight="1" s="4">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>ambiguitätstolerant</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" s="4">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>komplexitätsfreundlich</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="4">
-      <c r="A101" s="6" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>tiefgründig</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="15" customHeight="1" s="4">
-      <c r="A102" s="6" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>differenziert</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>sensemaker</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>